--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_ワーニングの確認結果_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_ワーニングの確認結果_20260925.xlsx
@@ -3077,7 +3077,7 @@
         <v>6104.306297738482</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>6095</v>
+        <v>6048</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>

--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_ワーニングの確認結果_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_ワーニングの確認結果_20260925.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>当方の訂正が正しかった</t>
+          <t>当方の算式と一致</t>
         </is>
       </c>
     </row>
